--- a/src/test/resources/AddCartPLT.xlsx
+++ b/src/test/resources/AddCartPLT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coder\Selenium\Totoday\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A516AFF9-49A7-4B7F-A4DE-A878E3C9F393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63A7A87-7F7F-4FC8-8DB2-73AAA1984DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E0B1910F-9E25-4940-9991-D9CB145F8934}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E0B1910F-9E25-4940-9991-D9CB145F8934}"/>
   </bookViews>
   <sheets>
     <sheet name="InforData" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="13">
   <si>
     <t>name</t>
   </si>
@@ -71,7 +71,10 @@
     <t>ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz123456</t>
   </si>
   <si>
-    <t>2</t>
+    <t>ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz123456234562345623456</t>
+  </si>
+  <si>
+    <t>aferyher</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4805CE63-B1A3-4A70-A6C7-7FBAE6F6C5A6}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="26.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="26.453125" style="2"/>
@@ -517,18 +520,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -536,14 +533,20 @@
     </row>
     <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -552,13 +555,30 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -566,7 +586,9 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{1FA7B84E-BA8D-46DE-830D-24C115708AEA}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{1E964747-3D9C-4BF6-BF83-30B2ADD47EB4}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{D2CEEBF6-4E14-429A-8E50-74DD1F989AB8}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{D2CEEBF6-4E14-429A-8E50-74DD1F989AB8}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{5A366FFF-AC99-44FC-B90A-A9D12F680D16}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{B25B5232-25FE-4CC8-BD9F-39A9FB452AC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/AddCartPLT.xlsx
+++ b/src/test/resources/AddCartPLT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coder\Selenium\Totoday\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63A7A87-7F7F-4FC8-8DB2-73AAA1984DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ABD6D1-E7E7-4DE2-97A2-464C315597BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E0B1910F-9E25-4940-9991-D9CB145F8934}"/>
+    <workbookView xWindow="-24170" yWindow="2380" windowWidth="21540" windowHeight="8450" xr2:uid="{E0B1910F-9E25-4940-9991-D9CB145F8934}"/>
   </bookViews>
   <sheets>
     <sheet name="InforData" sheetId="1" r:id="rId1"/>
